--- a/avance0403.xlsx
+++ b/avance0403.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LUCHO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B5F919-646C-4AAC-8469-88BDC6E91A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BE9D8C-F147-4FCB-8F74-C85B13D1C5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BD18AC21-6960-4AE2-8339-20D741B3F2ED}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$C$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$C$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -328,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,6 +355,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -691,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D23ADC3-8B94-4C89-9402-4892B6A0FB19}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="2" customWidth="1"/>
@@ -740,7 +746,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="4">
-        <v>374082</v>
+        <v>416265.13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -794,8 +800,8 @@
       <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5">
-        <v>91662.8</v>
+      <c r="C9" s="10">
+        <v>137494.20000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>78823.98000000001</v>
+        <v>136858.06</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -817,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="4">
-        <v>85101.15</v>
+        <v>140456.29999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -839,7 +845,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="4">
-        <v>368965.26</v>
+        <v>468465.26</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -872,7 +878,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="4">
-        <v>96607</v>
+        <v>193214</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1026,7 +1032,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="4">
-        <v>48033.93</v>
+        <v>136330.22</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1037,7 +1043,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="4">
-        <v>395393.22</v>
+        <v>474751.22</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1048,7 +1054,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="4">
-        <v>395030</v>
+        <v>474036</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1092,7 +1098,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="4">
-        <v>143600.17000000001</v>
+        <v>180309.16</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1169,7 +1175,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="8">
-        <v>197046</v>
+        <v>336614</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1326,7 +1332,13 @@
         <v>154810.5</v>
       </c>
     </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="11"/>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C57">
+    <sortCondition ref="A2:A57"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/avance0403.xlsx
+++ b/avance0403.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\LUCHO\docker\fondo\sistema-activa-t\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jduran\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E123D9-6263-4629-836C-EA5CBD3FB49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29A6BD1-1CA7-467F-A7AC-37ED1844EFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BD18AC21-6960-4AE2-8339-20D741B3F2ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BD18AC21-6960-4AE2-8339-20D741B3F2ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -45,17 +45,47 @@
     <t>codigo_proyecto</t>
   </si>
   <si>
-    <t>C-11-01</t>
-  </si>
-  <si>
     <t>avance</t>
+  </si>
+  <si>
+    <t>AT24-01</t>
+  </si>
+  <si>
+    <t>AT24-02</t>
+  </si>
+  <si>
+    <t>AT24-08</t>
+  </si>
+  <si>
+    <t>AT24-19</t>
+  </si>
+  <si>
+    <t>C-24-01</t>
+  </si>
+  <si>
+    <t>C-24-07</t>
+  </si>
+  <si>
+    <t>C-24-14</t>
+  </si>
+  <si>
+    <t>C-24-17</t>
+  </si>
+  <si>
+    <t>C-24-22</t>
+  </si>
+  <si>
+    <t>C-24-29</t>
+  </si>
+  <si>
+    <t>C-24-31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,19 +100,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -95,34 +119,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -141,37 +144,40 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -508,34 +514,144 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D23ADC3-8B94-4C89-9402-4892B6A0FB19}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>453</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4">
-        <v>15</v>
+      <c r="C2" s="2">
+        <v>240064</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>454</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="6">
+        <v>210730</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>460</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="6">
+        <v>235730</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>471</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6">
+        <v>262669.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>286</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="6">
+        <v>719226.57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>292</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6">
+        <v>140816.41999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>299</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>164598.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>302</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
+        <v>253377.27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>306</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="6">
+        <v>226152.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>313</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6">
+        <v>184777.36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>315</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="6">
+        <v>554289.22</v>
       </c>
     </row>
   </sheetData>
